--- a/descargas/factura-autonomo.xlsx
+++ b/descargas/factura-autonomo.xlsx
@@ -778,7 +778,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Rellena solo las celdas amarillas: el resto se calcula solo. Modelo orientativo de calculalotuyo.es. Revisa tu convenio colectivo, que puede mejorar lo que dice la ley.</t>
+          <t>Rellena solo las celdas amarillas: el resto se calcula solo.</t>
         </is>
       </c>
     </row>
